--- a/formxls/src/main/python/Relatorio_Vendas.xlsx
+++ b/formxls/src/main/python/Relatorio_Vendas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,60 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>jorge</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>negociando</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>davi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>fechado</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mieri</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D4" t="n">
-        <v>300</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
